--- a/videos_2.xlsx
+++ b/videos_2.xlsx
@@ -8,46 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/xxc/Desktop/xxc/拓殖大学/研究室/評価実験/video-recommend-system/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4286EA42-DED4-DD4B-861E-9798733FDA0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC2862EF-E216-4A47-B856-E6E8C23D4B66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14280" windowHeight="18000" xr2:uid="{E782D53B-1D4F-CD45-BA20-5FA0010CCCB3}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="14280" windowHeight="16000" xr2:uid="{E782D53B-1D4F-CD45-BA20-5FA0010CCCB3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId2"/>
-  </externalReferences>
-  <definedNames>
-    <definedName name="_xlchart.v1.0" hidden="1">Sheet1!$D$1</definedName>
-    <definedName name="_xlchart.v1.1" hidden="1">Sheet1!$D$2:$D$11</definedName>
-    <definedName name="_xlchart.v1.10" hidden="1">Sheet1!$I$1</definedName>
-    <definedName name="_xlchart.v1.11" hidden="1">Sheet1!$I$2:$I$11</definedName>
-    <definedName name="_xlchart.v1.12" hidden="1">Sheet1!$J$1</definedName>
-    <definedName name="_xlchart.v1.13" hidden="1">Sheet1!$J$2:$J$11</definedName>
-    <definedName name="_xlchart.v1.2" hidden="1">Sheet1!$E$1</definedName>
-    <definedName name="_xlchart.v1.3" hidden="1">Sheet1!$E$2:$E$11</definedName>
-    <definedName name="_xlchart.v1.4" hidden="1">Sheet1!$F$1</definedName>
-    <definedName name="_xlchart.v1.5" hidden="1">Sheet1!$F$2:$F$11</definedName>
-    <definedName name="_xlchart.v1.6" hidden="1">Sheet1!$G$1</definedName>
-    <definedName name="_xlchart.v1.7" hidden="1">Sheet1!$G$2:$G$11</definedName>
-    <definedName name="_xlchart.v1.8" hidden="1">Sheet1!$H$1</definedName>
-    <definedName name="_xlchart.v1.9" hidden="1">Sheet1!$H$2:$H$11</definedName>
-    <definedName name="_xlchart.v2.14" hidden="1">Sheet1!$D$1</definedName>
-    <definedName name="_xlchart.v2.15" hidden="1">Sheet1!$D$2:$D$11</definedName>
-    <definedName name="_xlchart.v2.16" hidden="1">Sheet1!$E$1</definedName>
-    <definedName name="_xlchart.v2.17" hidden="1">Sheet1!$E$2:$E$11</definedName>
-    <definedName name="_xlchart.v2.18" hidden="1">Sheet1!$F$1</definedName>
-    <definedName name="_xlchart.v2.19" hidden="1">Sheet1!$F$2:$F$11</definedName>
-    <definedName name="_xlchart.v2.20" hidden="1">Sheet1!$G$1</definedName>
-    <definedName name="_xlchart.v2.21" hidden="1">Sheet1!$G$2:$G$11</definedName>
-    <definedName name="_xlchart.v2.22" hidden="1">Sheet1!$H$1</definedName>
-    <definedName name="_xlchart.v2.23" hidden="1">Sheet1!$H$2:$H$11</definedName>
-    <definedName name="_xlchart.v2.24" hidden="1">Sheet1!$I$1</definedName>
-    <definedName name="_xlchart.v2.25" hidden="1">Sheet1!$I$2:$I$11</definedName>
-    <definedName name="_xlchart.v2.26" hidden="1">Sheet1!$J$1</definedName>
-    <definedName name="_xlchart.v2.27" hidden="1">Sheet1!$J$2:$J$11</definedName>
-  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -249,11 +216,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>meme,コメディ,文化,軍事,SLAV,ロシア,音楽</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>meme,コメディ,政治,音楽,Putin,ロシア</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>meme,コメディ,文化,軍事,SLAV,ロシア</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -353,69 +320,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Sheet1"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="1">
-          <cell r="D1" t="str">
-            <v>悲しい</v>
-          </cell>
-          <cell r="E1" t="str">
-            <v>不安</v>
-          </cell>
-          <cell r="F1" t="str">
-            <v>怒り</v>
-          </cell>
-          <cell r="G1" t="str">
-            <v>嫌悪</v>
-          </cell>
-          <cell r="H1" t="str">
-            <v>信頼</v>
-          </cell>
-          <cell r="I1" t="str">
-            <v>驚き</v>
-          </cell>
-          <cell r="J1" t="str">
-            <v>嬉しい</v>
-          </cell>
-        </row>
-        <row r="100">
-          <cell r="D100">
-            <v>0.40824829000000001</v>
-          </cell>
-          <cell r="E100">
-            <v>0.27216552700000002</v>
-          </cell>
-          <cell r="F100">
-            <v>0</v>
-          </cell>
-          <cell r="G100">
-            <v>0</v>
-          </cell>
-          <cell r="H100">
-            <v>0.40824829000000001</v>
-          </cell>
-          <cell r="I100">
-            <v>0.54433105400000004</v>
-          </cell>
-          <cell r="J100">
-            <v>0.54433105400000004</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1112,7 +1016,7 @@
         <v>0.61852799999999997</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L10" s="2" t="s">
         <v>45</v>
@@ -1150,7 +1054,7 @@
         <v>0.58675999999999995</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="L11" s="2" t="s">
         <v>47</v>

--- a/videos_2.xlsx
+++ b/videos_2.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC2862EF-E216-4A47-B856-E6E8C23D4B66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="14280" windowHeight="16000" xr2:uid="{E782D53B-1D4F-CD45-BA20-5FA0010CCCB3}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{E782D53B-1D4F-CD45-BA20-5FA0010CCCB3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
